--- a/data/trans_camb/DC-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/DC-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,3; -0,24</t>
+          <t>-10,67; -0,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 2,61</t>
+          <t>-8,61; 2,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 4,1</t>
+          <t>-6,51; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 12,42</t>
+          <t>-2,65; 12,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 12,28</t>
+          <t>-2,73; 11,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 7,53</t>
+          <t>-5,22; 7,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 4,8</t>
+          <t>-4,39; 4,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 5,45</t>
+          <t>-3,31; 5,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 4,13</t>
+          <t>-4,53; 3,82</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,13; 3,6</t>
+          <t>-64,29; 1,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,7; 25,61</t>
+          <t>-51,77; 27,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 41,32</t>
+          <t>-38,74; 50,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 72,51</t>
+          <t>-11,65; 77,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 68,65</t>
+          <t>-11,04; 69,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 44,68</t>
+          <t>-21,63; 45,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 32,84</t>
+          <t>-22,96; 32,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 36,59</t>
+          <t>-17,77; 38,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 28,44</t>
+          <t>-23,1; 26,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,01; -10,76</t>
+          <t>-19,95; -10,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -11,65</t>
+          <t>-20,7; -11,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 2,34</t>
+          <t>-8,72; 2,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -18,69</t>
+          <t>-30,41; -19,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,1; -28,14</t>
+          <t>-39,07; -28,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,38; -1,94</t>
+          <t>-13,32; -1,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,88; -16,56</t>
+          <t>-23,72; -16,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,32; -21,52</t>
+          <t>-28,64; -21,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -1,18</t>
+          <t>-9,72; -1,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,25; -54,4</t>
+          <t>-79,53; -54,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,93; -60,39</t>
+          <t>-82,15; -60,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 11,6</t>
+          <t>-35,6; 10,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,51; -45,06</t>
+          <t>-64,0; -45,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,07; -67,71</t>
+          <t>-81,32; -67,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,83; -4,48</t>
+          <t>-27,35; -2,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,75; -51,64</t>
+          <t>-66,61; -51,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,32; -67,45</t>
+          <t>-79,74; -68,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,89; -3,36</t>
+          <t>-26,76; -3,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 3,32</t>
+          <t>-6,39; 2,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 2,1</t>
+          <t>-6,23; 2,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 18,27</t>
+          <t>7,31; 18,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 4,69</t>
+          <t>-8,45; 4,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 3,56</t>
+          <t>-8,65; 3,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 21,31</t>
+          <t>9,13; 21,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 2,17</t>
+          <t>-5,28; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1,63</t>
+          <t>-6,44; 1,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 17,85</t>
+          <t>9,81; 18,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 40,35</t>
+          <t>-50,74; 37,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 29,14</t>
+          <t>-51,94; 32,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55,11; 236,99</t>
+          <t>53,13; 234,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 25,96</t>
+          <t>-34,02; 25,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 20,9</t>
+          <t>-35,51; 22,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,84; 116,16</t>
+          <t>34,79; 118,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 15,79</t>
+          <t>-30,56; 16,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 12,13</t>
+          <t>-36,14; 9,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,11; 129,19</t>
+          <t>53,42; 133,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,81; -3,05</t>
+          <t>-14,69; -3,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -4,26</t>
+          <t>-15,26; -4,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 4,07</t>
+          <t>-8,4; 4,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,64</t>
+          <t>-0,04; 11,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 8,97</t>
+          <t>-3,82; 8,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,72; 44,85</t>
+          <t>8,76; 43,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,77</t>
+          <t>-5,39; 2,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 0,25</t>
+          <t>-7,53; 0,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 30,63</t>
+          <t>3,57; 30,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -15,8</t>
+          <t>-61,65; -18,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,56; -23,43</t>
+          <t>-65,17; -23,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 23,34</t>
+          <t>-37,65; 23,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 62,81</t>
+          <t>-0,35; 63,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 46,68</t>
+          <t>-15,54; 47,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,46; 228,2</t>
+          <t>37,44; 230,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 15,19</t>
+          <t>-24,3; 15,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 1,33</t>
+          <t>-32,79; 3,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,11; 158,96</t>
+          <t>15,89; 154,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 16,07</t>
+          <t>3,93; 16,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 9,7</t>
+          <t>-1,25; 9,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,0; 17,03</t>
+          <t>6,05; 17,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,64; 29,39</t>
+          <t>12,1; 28,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 7,63</t>
+          <t>-7,12; 8,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 18,65</t>
+          <t>-6,04; 18,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,04; 20,63</t>
+          <t>9,44; 20,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,99</t>
+          <t>-2,61; 6,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 16,57</t>
+          <t>2,05; 16,4</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>28,57; 349,74</t>
+          <t>35,86; 382,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 206,69</t>
+          <t>-19,14; 209,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54,15; 354,83</t>
+          <t>56,19; 375,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49,51; 200,25</t>
+          <t>51,9; 200,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 50,39</t>
+          <t>-31,16; 56,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 115,6</t>
+          <t>-25,32; 110,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,12; 188,61</t>
+          <t>59,58; 193,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 65,7</t>
+          <t>-17,85; 64,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19,61; 148,5</t>
+          <t>19,81; 148,34</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 5,24</t>
+          <t>-7,25; 5,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,3; -0,1</t>
+          <t>-12,22; -0,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,72; 18,52</t>
+          <t>5,75; 18,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 7,22</t>
+          <t>-7,01; 7,64</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-18,33; -4,67</t>
+          <t>-18,7; -4,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,74; 23,76</t>
+          <t>9,39; 23,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 4,52</t>
+          <t>-5,51; 4,56</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,63; -4,14</t>
+          <t>-13,68; -4,62</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,38; 19,07</t>
+          <t>9,63; 18,82</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 42,75</t>
+          <t>-36,31; 44,38</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-62,12; 0,68</t>
+          <t>-61,49; 0,38</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30,24; 149,28</t>
+          <t>28,44; 149,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 31,37</t>
+          <t>-22,89; 33,51</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -19,85</t>
+          <t>-60,67; -19,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,62; 103,57</t>
+          <t>29,98; 105,54</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 22,86</t>
+          <t>-22,77; 24,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,56; -20,41</t>
+          <t>-56,62; -23,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37,79; 99,02</t>
+          <t>38,76; 98,42</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -0,28</t>
+          <t>-7,89; -0,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,91; -0,99</t>
+          <t>-9,22; -1,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,66; 19,82</t>
+          <t>9,9; 19,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,78</t>
+          <t>1,49; 11,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 6,08</t>
+          <t>-2,91; 6,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,68; 63,16</t>
+          <t>34,24; 63,11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,52</t>
+          <t>-1,89; 4,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 1,0</t>
+          <t>-4,97; 1,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24,4; 53,2</t>
+          <t>24,46; 50,96</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,19; -1,84</t>
+          <t>-43,04; -1,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,55; -8,92</t>
+          <t>-49,36; -8,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>53,04; 141,41</t>
+          <t>50,57; 138,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,12; 59,46</t>
+          <t>6,52; 62,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 33,48</t>
+          <t>-13,24; 33,64</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>165,37; 363,52</t>
+          <t>161,41; 356,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 26,9</t>
+          <t>-9,76; 26,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 5,89</t>
+          <t>-24,71; 7,78</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>127,43; 288,36</t>
+          <t>128,67; 305,59</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-17,12; -10,1</t>
+          <t>-17,17; -9,59</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -8,75</t>
+          <t>-16,35; -8,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -1,57</t>
+          <t>-16,32; -1,59</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,65; -11,77</t>
+          <t>-20,54; -11,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-23,17; -14,06</t>
+          <t>-22,72; -14,38</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,61</t>
+          <t>-5,95; 3,02</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-17,63; -11,88</t>
+          <t>-17,85; -11,9</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -12,64</t>
+          <t>-18,38; -12,79</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,96; -1,11</t>
+          <t>-15,56; -0,8</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-70,45; -49,28</t>
+          <t>-70,23; -47,58</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-66,06; -43,19</t>
+          <t>-66,92; -43,79</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,81; -7,74</t>
+          <t>-70,47; -7,19</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-56,36; -36,81</t>
+          <t>-56,78; -37,72</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-63,14; -44,81</t>
+          <t>-63,08; -44,86</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 11,56</t>
+          <t>-16,21; 9,43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-59,07; -44,55</t>
+          <t>-59,78; -45,12</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-62,07; -47,3</t>
+          <t>-61,58; -48,31</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-50,7; -4,3</t>
+          <t>-52,48; -2,95</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -5,44</t>
+          <t>-8,89; -5,59</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,59; -6,4</t>
+          <t>-9,89; -6,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,08</t>
+          <t>-1,78; 5,15</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,16; -2,0</t>
+          <t>-6,31; -1,93</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -7,47</t>
+          <t>-11,43; -7,31</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,71; 25,4</t>
+          <t>9,9; 25,26</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -4,23</t>
+          <t>-6,87; -4,06</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -7,44</t>
+          <t>-9,94; -7,31</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,53; 16,15</t>
+          <t>5,57; 15,07</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-47,45; -32,95</t>
+          <t>-47,94; -33,64</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-52,57; -37,94</t>
+          <t>-53,01; -38,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 30,35</t>
+          <t>-9,21; 30,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-21,15; -7,26</t>
+          <t>-21,42; -7,26</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-40,24; -28,01</t>
+          <t>-39,49; -27,42</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>34,71; 93,93</t>
+          <t>35,05; 92,26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-29,6; -19,24</t>
+          <t>-29,2; -18,1</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-42,51; -33,46</t>
+          <t>-42,64; -33,14</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>23,99; 70,52</t>
+          <t>23,81; 65,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DC-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/DC-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -0,12</t>
+          <t>-10,23; -0,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 2,67</t>
+          <t>-8,77; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,93</t>
+          <t>-6,17; 4,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 12,72</t>
+          <t>-2,31; 12,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 11,81</t>
+          <t>-2,31; 12,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 7,77</t>
+          <t>-5,72; 6,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,7</t>
+          <t>-5,29; 4,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,89</t>
+          <t>-3,22; 5,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 3,82</t>
+          <t>-3,78; 4,36</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-7,25%</t>
+          <t>-5,32%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 1,48</t>
+          <t>-64,42; -0,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 27,06</t>
+          <t>-52,78; 28,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 50,15</t>
+          <t>-38,71; 44,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 77,89</t>
+          <t>-9,84; 76,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 69,5</t>
+          <t>-9,73; 72,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 45,56</t>
+          <t>-21,48; 37,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 32,29</t>
+          <t>-26,45; 30,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 38,37</t>
+          <t>-17,15; 38,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 26,36</t>
+          <t>-19,6; 29,84</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,22</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,62</t>
+          <t>-8,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,57</t>
+          <t>-5,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,95; -10,86</t>
+          <t>-19,89; -10,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,7; -11,79</t>
+          <t>-20,39; -11,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 2,15</t>
+          <t>-8,33; 2,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,41; -19,37</t>
+          <t>-30,64; -19,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,07; -28,81</t>
+          <t>-39,15; -28,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,32; -1,06</t>
+          <t>-13,49; -2,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -16,21</t>
+          <t>-23,99; -16,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,64; -21,65</t>
+          <t>-28,31; -21,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -1,21</t>
+          <t>-9,84; -1,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-14,53%</t>
+          <t>-13,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-16,99%</t>
+          <t>-17,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,57%</t>
+          <t>-16,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,53; -54,27</t>
+          <t>-79,0; -53,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,15; -60,33</t>
+          <t>-81,01; -60,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 10,68</t>
+          <t>-33,48; 12,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,0; -45,11</t>
+          <t>-63,76; -45,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,32; -67,36</t>
+          <t>-81,04; -67,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,35; -2,45</t>
+          <t>-27,94; -4,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,61; -51,5</t>
+          <t>-66,61; -52,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,74; -68,33</t>
+          <t>-79,39; -68,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,76; -3,77</t>
+          <t>-27,12; -5,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,6</t>
+          <t>12,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,17</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,08</t>
+          <t>14,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,74</t>
+          <t>-5,88; 2,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 2,4</t>
+          <t>-6,57; 2,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,31; 18,19</t>
+          <t>7,38; 18,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 4,49</t>
+          <t>-7,6; 4,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 3,95</t>
+          <t>-8,61; 4,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 21,46</t>
+          <t>9,51; 21,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 2,35</t>
+          <t>-5,37; 2,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 1,36</t>
+          <t>-6,01; 1,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 18,43</t>
+          <t>10,44; 18,35</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124,37%</t>
+          <t>125,16%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 37,95</t>
+          <t>-49,09; 36,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 32,15</t>
+          <t>-52,56; 34,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,13; 234,7</t>
+          <t>52,78; 218,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,02; 25,3</t>
+          <t>-31,08; 25,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 22,6</t>
+          <t>-36,67; 20,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,79; 118,37</t>
+          <t>37,37; 118,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 16,73</t>
+          <t>-30,49; 20,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 9,12</t>
+          <t>-34,17; 11,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,42; 133,35</t>
+          <t>57,92; 134,08</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,87</t>
+          <t>13,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>5,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -3,26</t>
+          <t>-14,25; -3,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -4,36</t>
+          <t>-14,88; -4,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 4,05</t>
+          <t>-10,29; 1,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 11,86</t>
+          <t>-1,01; 11,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 8,55</t>
+          <t>-4,29; 8,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 43,35</t>
+          <t>7,58; 19,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 2,85</t>
+          <t>-5,42; 3,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 0,61</t>
+          <t>-7,68; 0,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 30,41</t>
+          <t>0,74; 9,61</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-13,08%</t>
+          <t>-22,56%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,65; -18,87</t>
+          <t>-59,92; -18,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,17; -23,8</t>
+          <t>-63,98; -21,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 23,8</t>
+          <t>-44,95; 6,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 63,52</t>
+          <t>-4,5; 62,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 47,81</t>
+          <t>-16,72; 44,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,44; 230,9</t>
+          <t>30,4; 104,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 15,5</t>
+          <t>-23,23; 17,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 3,38</t>
+          <t>-33,13; 4,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,89; 154,72</t>
+          <t>3,01; 50,59</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,59</t>
+          <t>10,91</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,16</t>
+          <t>13,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,93; 16,58</t>
+          <t>3,76; 16,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 9,68</t>
+          <t>-1,81; 9,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,05; 17,68</t>
+          <t>5,24; 16,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,1; 28,79</t>
+          <t>11,89; 29,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 8,88</t>
+          <t>-7,56; 7,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 18,36</t>
+          <t>7,75; 21,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,44; 20,49</t>
+          <t>9,69; 21,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 6,92</t>
+          <t>-2,62; 7,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 16,4</t>
+          <t>8,6; 18,03</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163,65%</t>
+          <t>154,15%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>100,28%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>35,86; 382,25</t>
+          <t>33,67; 351,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 209,47</t>
+          <t>-24,03; 181,57</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56,19; 375,91</t>
+          <t>51,38; 358,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51,9; 200,87</t>
+          <t>50,88; 199,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 56,33</t>
+          <t>-32,8; 53,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 110,71</t>
+          <t>30,82; 147,54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,58; 193,19</t>
+          <t>58,92; 194,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 64,74</t>
+          <t>-17,73; 68,08</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19,81; 148,34</t>
+          <t>51,69; 169,58</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>11,7</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,64</t>
+          <t>16,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>13,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 5,6</t>
+          <t>-6,61; 5,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -0,25</t>
+          <t>-12,05; -0,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,75; 18,91</t>
+          <t>5,11; 17,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 7,64</t>
+          <t>-7,03; 7,41</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-18,7; -4,49</t>
+          <t>-18,4; -4,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,39; 23,92</t>
+          <t>8,91; 22,93</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,56</t>
+          <t>-5,69; 4,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -4,62</t>
+          <t>-13,34; -4,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,63; 18,82</t>
+          <t>8,92; 18,45</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-36,31; 44,38</t>
+          <t>-36,55; 46,59</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-61,49; 0,38</t>
+          <t>-63,43; -1,11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28,44; 149,15</t>
+          <t>23,44; 137,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 33,51</t>
+          <t>-23,72; 31,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -19,49</t>
+          <t>-61,38; -20,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,98; 105,54</t>
+          <t>28,9; 102,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 24,72</t>
+          <t>-23,49; 21,73</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-56,62; -23,25</t>
+          <t>-55,27; -22,65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38,76; 98,42</t>
+          <t>37,39; 94,87</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>14,89</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,48</t>
+          <t>36,58</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>33,35</t>
+          <t>26,15</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -0,35</t>
+          <t>-7,64; 0,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -1,22</t>
+          <t>-9,0; -1,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,9; 19,99</t>
+          <t>9,58; 19,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,49; 11,15</t>
+          <t>1,42; 11,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 6,17</t>
+          <t>-3,23; 5,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,24; 63,11</t>
+          <t>32,03; 41,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 4,3</t>
+          <t>-1,77; 4,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 1,28</t>
+          <t>-5,1; 1,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24,46; 50,96</t>
+          <t>22,62; 29,66</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>228,94%</t>
+          <t>180,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>182,01%</t>
+          <t>142,74%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-43,04; -1,21</t>
+          <t>-43,19; 1,1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-49,36; -8,18</t>
+          <t>-50,51; -8,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>50,57; 138,45</t>
+          <t>52,55; 137,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,52; 62,23</t>
+          <t>6,33; 60,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 33,64</t>
+          <t>-14,52; 31,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>161,41; 356,65</t>
+          <t>137,44; 234,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 26,03</t>
+          <t>-9,28; 25,91</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 7,78</t>
+          <t>-25,34; 6,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>128,67; 305,59</t>
+          <t>112,61; 180,53</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-8,11</t>
+          <t>-3,66</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-1,73</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,97</t>
+          <t>-2,71</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -9,59</t>
+          <t>-16,88; -9,87</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,35; -8,69</t>
+          <t>-16,49; -8,97</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,32; -1,59</t>
+          <t>-7,9; 0,24</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,54; -11,79</t>
+          <t>-20,13; -11,47</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-22,72; -14,38</t>
+          <t>-22,79; -14,15</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,02</t>
+          <t>-6,07; 2,64</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-17,85; -11,9</t>
+          <t>-17,62; -11,95</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-18,38; -12,79</t>
+          <t>-18,72; -12,87</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -0,8</t>
+          <t>-5,58; 0,5</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-36,58%</t>
+          <t>-16,48%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-3,35%</t>
+          <t>-5,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-21,2%</t>
+          <t>-9,62%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-70,23; -47,58</t>
+          <t>-70,23; -48,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-66,92; -43,79</t>
+          <t>-67,25; -45,01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-70,47; -7,19</t>
+          <t>-32,87; 1,32</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-56,78; -37,72</t>
+          <t>-56,35; -36,96</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-63,08; -44,86</t>
+          <t>-63,54; -45,75</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 9,43</t>
+          <t>-16,62; 8,63</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-59,78; -45,12</t>
+          <t>-59,45; -44,8</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-61,58; -48,31</t>
+          <t>-62,14; -48,61</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-52,48; -2,95</t>
+          <t>-18,64; 1,89</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>10,91</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>7,58</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -5,59</t>
+          <t>-8,94; -5,53</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -6,41</t>
+          <t>-9,69; -6,46</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,15</t>
+          <t>1,93; 5,77</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -1,93</t>
+          <t>-6,32; -1,96</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -7,31</t>
+          <t>-11,56; -7,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,9; 25,26</t>
+          <t>9,05; 13,09</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-6,87; -4,06</t>
+          <t>-6,96; -4,2</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -7,31</t>
+          <t>-9,97; -7,41</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,57; 15,07</t>
+          <t>6,15; 9,08</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-47,94; -33,64</t>
+          <t>-48,6; -33,0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-53,01; -38,23</t>
+          <t>-52,57; -38,16</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 30,8</t>
+          <t>10,59; 34,77</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -7,26</t>
+          <t>-21,6; -7,21</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -27,42</t>
+          <t>-39,64; -27,54</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>35,05; 92,26</t>
+          <t>31,36; 48,94</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-29,2; -18,1</t>
+          <t>-29,47; -18,92</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-42,64; -33,14</t>
+          <t>-42,53; -33,43</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>23,81; 65,41</t>
+          <t>26,1; 41,19</t>
         </is>
       </c>
     </row>
